--- a/human_resources_forms/014_part_time_employee_offboarding_form--human_resources_forms.xlsx
+++ b/human_resources_forms/014_part_time_employee_offboarding_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,10 +437,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>exit_date</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Exit Date</t>
+          <t>Job Title</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>reason_for_leaving</t>
+          <t>job_type</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reason for Leaving</t>
+          <t>Job Type</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>next_step</t>
+          <t>notice_period</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Next Step</t>
+          <t>Notice Period</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>exit_date</t>
+          <t>last_day_of_work</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Exit Date</t>
+          <t>Last Day of Work</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,67 +699,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>reason_for_leaving</t>
+          <t>termination_reason</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reason for Leaving</t>
+          <t>Termination Reason</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>next_step</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Next Step</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>exit_date</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Exit Date</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -776,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'option1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'option1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -826,80 +780,97 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'option2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'option2', 'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>next_step_choices</t>
+          <t>job_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'option2',_'value':_'option2'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'option2', 'value': 'option2'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>next_step_choices</t>
+          <t>job_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'option1',_'value':_'option1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'option1', 'value': 'option1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>next_step_choices</t>
+          <t>termination_reason_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'option1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'option1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>next_step_choices</t>
+          <t>termination_reason_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'option2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'option2', 'value': 'option2'}</t>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>termination_reason_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
